--- a/data/trans_bre/P6904-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 38,91</t>
+          <t>-12,42; 41,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-43,69; 39,17</t>
+          <t>-46,17; 45,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,19; 53,18</t>
+          <t>-16,74; 53,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-71,02; 59,47</t>
+          <t>-69,47; 58,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 107,08</t>
+          <t>-21,8; 118,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,75; 409,81</t>
+          <t>-76,34; 345,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,93; 190,32</t>
+          <t>-28,56; 188,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-87,96; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 8,23</t>
+          <t>-20,91; 8,17</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,31; 9,11</t>
+          <t>-25,64; 8,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 21,55</t>
+          <t>-13,79; 20,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 13,7</t>
+          <t>-32,14; 10,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 19,86</t>
+          <t>-39,72; 19,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 18,82</t>
+          <t>-41,75; 18,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 43,36</t>
+          <t>-20,51; 41,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,96; 28,58</t>
+          <t>-44,26; 21,75</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 13,34</t>
+          <t>-16,15; 14,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-18,96; 12,95</t>
+          <t>-17,33; 12,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,88; 14,22</t>
+          <t>-15,21; 14,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 11,15</t>
+          <t>-17,73; 9,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,71; 25,64</t>
+          <t>-24,72; 27,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-29,54; 25,02</t>
+          <t>-27,38; 24,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-23,03; 24,48</t>
+          <t>-21,15; 25,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,66; 22,65</t>
+          <t>-26,33; 18,78</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 34,25</t>
+          <t>-2,39; 33,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-22,75; 15,96</t>
+          <t>-24,17; 13,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 26,23</t>
+          <t>-8,57; 24,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 29,51</t>
+          <t>-0,58; 30,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 81,39</t>
+          <t>-3,9; 81,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,68; 36,19</t>
+          <t>-44,57; 31,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 56,31</t>
+          <t>-13,47; 51,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 53,05</t>
+          <t>-1,25; 57,31</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-57,44; -7,41</t>
+          <t>-57,87; -3,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 33,98</t>
+          <t>-16,88; 32,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,79; 42,56</t>
+          <t>-0,37; 38,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 22,04</t>
+          <t>-7,57; 20,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-88,36; -12,05</t>
+          <t>-88,3; -4,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 75,45</t>
+          <t>-25,42; 69,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66; 81,61</t>
+          <t>1,6; 78,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 42,34</t>
+          <t>-10,76; 39,26</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-39,78; 82,17</t>
+          <t>-37,34; 73,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-45,39; 1738,99</t>
+          <t>-49,8; 593,19</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 7,74</t>
+          <t>-8,75; 8,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 5,03</t>
+          <t>-11,66; 5,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 16,18</t>
+          <t>-0,49; 16,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 15,77</t>
+          <t>-4,16; 16,37</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 15,39</t>
+          <t>-15,95; 17,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,0; 9,79</t>
+          <t>-20,07; 10,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 29,22</t>
+          <t>-0,73; 29,48</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 27,33</t>
+          <t>-6,62; 29,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P6904-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P6904-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,52</t>
+          <t>-13,45</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>-24,32%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 41,41</t>
+          <t>-13,61; 36,65</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-46,17; 45,1</t>
+          <t>-48,35; 38,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,74; 53,32</t>
+          <t>-21,7; 51,87</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-69,47; 58,6</t>
+          <t>-70,78; 48,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 118,57</t>
+          <t>-23,88; 95,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,34; 345,45</t>
+          <t>-82,31; 264,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 188,55</t>
+          <t>-29,18; 204,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-87,96; —</t>
+          <t>-82,73; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-10,57</t>
+          <t>-9,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-16,94%</t>
+          <t>-15,26%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,91; 8,17</t>
+          <t>-19,83; 8,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-25,64; 8,51</t>
+          <t>-26,88; 8,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 20,91</t>
+          <t>-14,83; 21,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 10,2</t>
+          <t>-30,95; 12,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,72; 19,37</t>
+          <t>-36,98; 18,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 18,0</t>
+          <t>-42,46; 17,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,51; 41,74</t>
+          <t>-22,42; 42,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-44,26; 21,75</t>
+          <t>-42,66; 25,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-3,14</t>
+          <t>-6,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-5,18%</t>
+          <t>-10,54%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 14,61</t>
+          <t>-14,69; 14,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 12,45</t>
+          <t>-17,77; 13,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 14,31</t>
+          <t>-13,36; 15,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-17,73; 9,89</t>
+          <t>-19,22; 6,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 27,72</t>
+          <t>-23,13; 26,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,38; 24,28</t>
+          <t>-28,58; 26,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,15; 25,14</t>
+          <t>-19,53; 25,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,33; 18,78</t>
+          <t>-28,12; 11,56</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,15</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 33,47</t>
+          <t>-3,91; 35,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-24,17; 13,77</t>
+          <t>-23,95; 14,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 24,98</t>
+          <t>-9,61; 26,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 30,04</t>
+          <t>-9,98; 11,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-3,9; 81,12</t>
+          <t>-6,5; 85,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,57; 31,55</t>
+          <t>-44,24; 30,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 51,9</t>
+          <t>-15,69; 56,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 57,31</t>
+          <t>-13,74; 19,75</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,77</t>
+          <t>5,02</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-57,87; -3,77</t>
+          <t>-57,16; -0,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 32,31</t>
+          <t>-15,85; 32,45</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 38,69</t>
+          <t>-0,71; 42,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 20,99</t>
+          <t>-9,19; 19,08</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-88,3; -4,07</t>
+          <t>-88,85; -0,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,42; 69,66</t>
+          <t>-25,02; 68,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,6; 78,07</t>
+          <t>-0,05; 86,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,76; 39,26</t>
+          <t>-12,68; 35,69</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22,79</t>
+          <t>15,6</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,34; 73,07</t>
+          <t>-40,39; 70,54</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,8; 593,19</t>
+          <t>-43,88; —</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,79</t>
+          <t>-2,31</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>-3,65%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 8,36</t>
+          <t>-8,72; 7,71</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-11,66; 5,43</t>
+          <t>-12,06; 5,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 16,47</t>
+          <t>-1,05; 15,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 16,37</t>
+          <t>-9,12; 4,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-15,95; 17,22</t>
+          <t>-15,42; 15,7</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,07; 10,93</t>
+          <t>-20,8; 11,88</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 29,48</t>
+          <t>-1,7; 28,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 29,39</t>
+          <t>-13,64; 7,32</t>
         </is>
       </c>
     </row>
